--- a/termine.xlsx
+++ b/termine.xlsx
@@ -231,24 +231,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -446,241 +450,241 @@
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="34.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="34.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>45429</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>45450</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>45493</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>45542</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>45563</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>45583</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>45617</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>45641</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>45836</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>45836</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>45844</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>45909</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="n">
-        <v>45917</v>
-      </c>
-      <c r="B14" s="3" t="s">
+      <c r="A14" s="3" t="n">
+        <v>45921</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>45920</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="4" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>45948</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>45955</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>45998</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="4" t="s">
         <v>26</v>
       </c>
     </row>

--- a/termine.xlsx
+++ b/termine.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="41">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -140,6 +140,9 @@
   </si>
   <si>
     <t xml:space="preserve">5500 Bischofshofen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5450 Werfen</t>
   </si>
 </sst>
 </file>
@@ -231,7 +234,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -254,6 +257,10 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -446,7 +453,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.57"/>
@@ -685,6 +692,17 @@
         <v>34</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="n">
+        <v>46004</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>26</v>
       </c>
     </row>

--- a/termine.xlsx
+++ b/termine.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -140,6 +140,9 @@
   </si>
   <si>
     <t xml:space="preserve">5500 Bischofshofen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.radstadt.at/Alpenlaendisches_Adventsingen</t>
   </si>
   <si>
     <t xml:space="preserve">5450 Werfen</t>
@@ -259,7 +262,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -694,13 +697,16 @@
       <c r="C18" s="4" t="s">
         <v>26</v>
       </c>
+      <c r="D18" s="0" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="n">
         <v>46004</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>26</v>

--- a/termine.xlsx
+++ b/termine.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="44">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -146,15 +146,22 @@
   </si>
   <si>
     <t xml:space="preserve">5450 Werfen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5541 Altenmarkt-Zauchensee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.altenmarkt-zauchensee.at/de/winter-urlaub/advent-markt.html</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yy"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -237,7 +244,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -259,11 +266,23 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -456,7 +475,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.57"/>
@@ -697,7 +716,7 @@
       <c r="C18" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="6" t="s">
         <v>40</v>
       </c>
     </row>
@@ -705,11 +724,25 @@
       <c r="A19" s="3" t="n">
         <v>46004</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>41</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="n">
+        <v>46005</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/termine.xlsx
+++ b/termine.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Debian\home\karin\private\almstueberlmusi.at\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A918FA-4218-41CB-ACEC-22D18C05FE28}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8964" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabellenblatt1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Tabellenblatt1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -20,185 +25,183 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="44">
-  <si>
-    <t xml:space="preserve">date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">details</t>
-  </si>
-  <si>
-    <t xml:space="preserve">url</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94209 Regen; Bayern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drumherum – Das Volksmusikspektakel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.drumherum.com/teilnehmer/musikanten/teilnehmer-2024-98.html?gruppe=0226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5524 Annaberg im Lammertal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rottenhofhütte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.rottenhofhuette.at/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5020 Salzburg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salzburger Straßenmusik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.salzburgervolksliedwerk.at/fileadmin/user_upload/volksliedwerk/user_upload/Folder_Salzburger_Strassenmusik_2024_web.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8966 Aich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aicher Kirchtag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.aicher-herbst-kultur.at/Aicher_Kirtag/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5524 Annaberg im Lammertal; Winterstellgut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hochzeit (privat)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.tauroa.at/de/winterstellgut/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5453 Werfenweng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Werfenwenger Weis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.salzburgerland.com/de/werfenweng/veranstaltungen/SBG/ff809fc9-ee1b-4036-82a1-35f154d0332f/werfenwenger-herbst-weis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5620 Schwarzach im Pongau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weihnachtsfeier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.gde-schwarzach.salzburg.at/Seniorenzentrum_Schwarzach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5451 Tenneck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adventkonzert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.salzburgervolksliedwerk.at/termine/detail?tx_calendarize_calendar%5Baction%5D=detail&amp;tx_calendarize_calendar%5Bcontroller%5D=Calendar&amp;tx_calendarize_calendar%5Bindex%5D=103822&amp;cHash=3b0ade89f12374e9bdde86e47b10ff89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5611 Großarl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alm-Musi-Roas: Rottenhofhütte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.dachstein.at/de/aktuelles/events/alm-musi-roas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5542 Flachau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stammgäste-Galaabend im Tirolerhof</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.hotel-tirolerhof.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5550 Radstadt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erntedankfest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.radstadt.com/radstadt/veranstaltungskalender/veranstaltungen/SPO/5daeaf0a-c467-4911-8642-9265a620dec0/roem--kath--erntedankfest-mit-prozession</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Musikantenstammtisch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5661 Rauris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5500 Bischofshofen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.radstadt.at/Alpenlaendisches_Adventsingen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5450 Werfen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5541 Altenmarkt-Zauchensee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.altenmarkt-zauchensee.at/de/winter-urlaub/advent-markt.html</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="50">
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>details</t>
+  </si>
+  <si>
+    <t>url</t>
+  </si>
+  <si>
+    <t>94209 Regen; Bayern</t>
+  </si>
+  <si>
+    <t>drumherum – Das Volksmusikspektakel</t>
+  </si>
+  <si>
+    <t>https://www.drumherum.com/teilnehmer/musikanten/teilnehmer-2024-98.html?gruppe=0226</t>
+  </si>
+  <si>
+    <t>5524 Annaberg im Lammertal</t>
+  </si>
+  <si>
+    <t>Rottenhofhütte</t>
+  </si>
+  <si>
+    <t>https://www.rottenhofhuette.at/</t>
+  </si>
+  <si>
+    <t>5020 Salzburg</t>
+  </si>
+  <si>
+    <t>Salzburger Straßenmusik</t>
+  </si>
+  <si>
+    <t>https://www.salzburgervolksliedwerk.at/fileadmin/user_upload/volksliedwerk/user_upload/Folder_Salzburger_Strassenmusik_2024_web.pdf</t>
+  </si>
+  <si>
+    <t>8966 Aich</t>
+  </si>
+  <si>
+    <t>Aicher Kirchtag</t>
+  </si>
+  <si>
+    <t>https://www.aicher-herbst-kultur.at/Aicher_Kirtag/</t>
+  </si>
+  <si>
+    <t>5524 Annaberg im Lammertal; Winterstellgut</t>
+  </si>
+  <si>
+    <t>Hochzeit (privat)</t>
+  </si>
+  <si>
+    <t>https://www.tauroa.at/de/winterstellgut/</t>
+  </si>
+  <si>
+    <t>5453 Werfenweng</t>
+  </si>
+  <si>
+    <t>Werfenwenger Weis</t>
+  </si>
+  <si>
+    <t>https://www.salzburgerland.com/de/werfenweng/veranstaltungen/SBG/ff809fc9-ee1b-4036-82a1-35f154d0332f/werfenwenger-herbst-weis</t>
+  </si>
+  <si>
+    <t>5620 Schwarzach im Pongau</t>
+  </si>
+  <si>
+    <t>Weihnachtsfeier</t>
+  </si>
+  <si>
+    <t>https://www.gde-schwarzach.salzburg.at/Seniorenzentrum_Schwarzach</t>
+  </si>
+  <si>
+    <t>5451 Tenneck</t>
+  </si>
+  <si>
+    <t>Adventkonzert</t>
+  </si>
+  <si>
+    <t>https://www.salzburgervolksliedwerk.at/termine/detail?tx_calendarize_calendar%5Baction%5D=detail&amp;tx_calendarize_calendar%5Bcontroller%5D=Calendar&amp;tx_calendarize_calendar%5Bindex%5D=103822&amp;cHash=3b0ade89f12374e9bdde86e47b10ff89</t>
+  </si>
+  <si>
+    <t>5611 Großarl</t>
+  </si>
+  <si>
+    <t>Alm-Musi-Roas: Rottenhofhütte</t>
+  </si>
+  <si>
+    <t>https://www.dachstein.at/de/aktuelles/events/alm-musi-roas</t>
+  </si>
+  <si>
+    <t>5542 Flachau</t>
+  </si>
+  <si>
+    <t>Stammgäste-Galaabend im Tirolerhof</t>
+  </si>
+  <si>
+    <t>https://www.hotel-tirolerhof.com/</t>
+  </si>
+  <si>
+    <t>5550 Radstadt</t>
+  </si>
+  <si>
+    <t>Erntedankfest</t>
+  </si>
+  <si>
+    <t>https://www.radstadt.com/radstadt/veranstaltungskalender/veranstaltungen/SPO/5daeaf0a-c467-4911-8642-9265a620dec0/roem--kath--erntedankfest-mit-prozession</t>
+  </si>
+  <si>
+    <t>Musikantenstammtisch</t>
+  </si>
+  <si>
+    <t>5661 Rauris</t>
+  </si>
+  <si>
+    <t>5500 Bischofshofen</t>
+  </si>
+  <si>
+    <t>https://www.radstadt.at/Alpenlaendisches_Adventsingen</t>
+  </si>
+  <si>
+    <t>5450 Werfen</t>
+  </si>
+  <si>
+    <t>5541 Altenmarkt-Zauchensee</t>
+  </si>
+  <si>
+    <t>https://www.altenmarkt-zauchensee.at/de/winter-urlaub/advent-markt.html</t>
+  </si>
+  <si>
+    <t>Adventmarkt</t>
+  </si>
+  <si>
+    <t>5700 Zell am See</t>
+  </si>
+  <si>
+    <t>Zeller Adventkonzert des KIWANIS Club Zell am See</t>
+  </si>
+  <si>
+    <t>https://www.zellamsee-kaprun.com/de/event/zeller-adventkonzert-des-kiwanis-club-zell-am-see~12225</t>
+  </si>
+  <si>
+    <t>Weihnachtswanderung</t>
+  </si>
+  <si>
+    <t>https://www.radstadt.com/radstadt/top-events/weihnachts-wanderungen/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
-    <numFmt numFmtId="166" formatCode="dd/mm/yy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -211,7 +214,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -219,135 +222,90 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285f4"/>
+        <a:srgbClr val="4285F4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ea4335"/>
+        <a:srgbClr val="EA4335"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="fbbc04"/>
+        <a:srgbClr val="FBBC04"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34a853"/>
+        <a:srgbClr val="34A853"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="ff6d01"/>
+        <a:srgbClr val="FF6D01"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46bdc6"/>
+        <a:srgbClr val="46BDC6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155cc"/>
+        <a:srgbClr val="1155CC"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155cc"/>
+        <a:srgbClr val="1155CC"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -377,7 +335,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -401,7 +359,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -461,29 +419,30 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
     <outlinePr summaryBelow="0"/>
-    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="34.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="34.57"/>
+    <col min="1" max="1" width="12.5546875" style="1"/>
+    <col min="2" max="2" width="34.88671875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="34.5546875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -497,8 +456,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>45429</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -511,8 +470,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+    <row r="3" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>45450</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -525,8 +484,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+    <row r="4" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
         <v>45493</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -539,8 +498,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+    <row r="5" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
         <v>45542</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -553,8 +512,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
+    <row r="6" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
         <v>45563</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -567,8 +526,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
+    <row r="7" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
         <v>45583</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -581,8 +540,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
+    <row r="8" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
         <v>45617</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -595,8 +554,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
+    <row r="9" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
         <v>45641</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -606,8 +565,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="n">
+    <row r="10" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
         <v>45836</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -620,8 +579,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="n">
+    <row r="11" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
         <v>45836</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -631,8 +590,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="n">
+    <row r="12" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
         <v>45844</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -645,8 +604,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="n">
+    <row r="13" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
         <v>45909</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -659,8 +618,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="n">
+    <row r="14" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
         <v>45921</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -673,8 +632,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="n">
+    <row r="15" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
         <v>45920</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -684,8 +643,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="n">
+    <row r="16" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
         <v>45948</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -695,8 +654,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="n">
+    <row r="17" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
         <v>45955</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -706,63 +665,100 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="n">
+    <row r="18" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
         <v>45998</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>45998</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="n">
-        <v>46004</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>41</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="n">
-        <v>46005</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>42</v>
+      <c r="D19" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>46004</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="9" t="s">
+    </row>
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="8">
+        <v>46005</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>46005</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>46017</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" display="https://www.drumherum.com/teilnehmer/musikanten/teilnehmer-2024-98.html?gruppe=0226"/>
-    <hyperlink ref="D3" r:id="rId2" display="https://www.rottenhofhuette.at/"/>
-    <hyperlink ref="D4" r:id="rId3" display="https://www.salzburgervolksliedwerk.at/fileadmin/user_upload/volksliedwerk/user_upload/Folder_Salzburger_Strassenmusik_2024_web.pdf"/>
-    <hyperlink ref="D5" r:id="rId4" display="https://www.aicher-herbst-kultur.at/Aicher_Kirtag/"/>
-    <hyperlink ref="D6" r:id="rId5" display="https://www.tauroa.at/de/winterstellgut/"/>
-    <hyperlink ref="D7" r:id="rId6" display="https://www.salzburgerland.com/de/werfenweng/veranstaltungen/SBG/ff809fc9-ee1b-4036-82a1-35f154d0332f/werfenwenger-herbst-weis"/>
-    <hyperlink ref="D8" r:id="rId7" display="https://www.gde-schwarzach.salzburg.at/Seniorenzentrum_Schwarzach"/>
-    <hyperlink ref="D10" r:id="rId8" display="https://www.salzburgervolksliedwerk.at/termine/detail?tx_calendarize_calendar%5Baction%5D=detail&amp;tx_calendarize_calendar%5Bcontroller%5D=Calendar&amp;tx_calendarize_calendar%5Bindex%5D=103822&amp;cHash=3b0ade89f12374e9bdde86e47b10ff89"/>
-    <hyperlink ref="D12" r:id="rId9" display="https://www.dachstein.at/de/aktuelles/events/alm-musi-roas"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D10" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="D12" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
   </hyperlinks>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/termine.xlsx
+++ b/termine.xlsx
@@ -1,21 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Debian\home\karin\private\almstueberlmusi.at\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A918FA-4218-41CB-ACEC-22D18C05FE28}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8964" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabellenblatt1" sheetId="1" r:id="rId1"/>
+    <sheet name="Tabellenblatt1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -25,183 +20,205 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="50">
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>location</t>
-  </si>
-  <si>
-    <t>details</t>
-  </si>
-  <si>
-    <t>url</t>
-  </si>
-  <si>
-    <t>94209 Regen; Bayern</t>
-  </si>
-  <si>
-    <t>drumherum – Das Volksmusikspektakel</t>
-  </si>
-  <si>
-    <t>https://www.drumherum.com/teilnehmer/musikanten/teilnehmer-2024-98.html?gruppe=0226</t>
-  </si>
-  <si>
-    <t>5524 Annaberg im Lammertal</t>
-  </si>
-  <si>
-    <t>Rottenhofhütte</t>
-  </si>
-  <si>
-    <t>https://www.rottenhofhuette.at/</t>
-  </si>
-  <si>
-    <t>5020 Salzburg</t>
-  </si>
-  <si>
-    <t>Salzburger Straßenmusik</t>
-  </si>
-  <si>
-    <t>https://www.salzburgervolksliedwerk.at/fileadmin/user_upload/volksliedwerk/user_upload/Folder_Salzburger_Strassenmusik_2024_web.pdf</t>
-  </si>
-  <si>
-    <t>8966 Aich</t>
-  </si>
-  <si>
-    <t>Aicher Kirchtag</t>
-  </si>
-  <si>
-    <t>https://www.aicher-herbst-kultur.at/Aicher_Kirtag/</t>
-  </si>
-  <si>
-    <t>5524 Annaberg im Lammertal; Winterstellgut</t>
-  </si>
-  <si>
-    <t>Hochzeit (privat)</t>
-  </si>
-  <si>
-    <t>https://www.tauroa.at/de/winterstellgut/</t>
-  </si>
-  <si>
-    <t>5453 Werfenweng</t>
-  </si>
-  <si>
-    <t>Werfenwenger Weis</t>
-  </si>
-  <si>
-    <t>https://www.salzburgerland.com/de/werfenweng/veranstaltungen/SBG/ff809fc9-ee1b-4036-82a1-35f154d0332f/werfenwenger-herbst-weis</t>
-  </si>
-  <si>
-    <t>5620 Schwarzach im Pongau</t>
-  </si>
-  <si>
-    <t>Weihnachtsfeier</t>
-  </si>
-  <si>
-    <t>https://www.gde-schwarzach.salzburg.at/Seniorenzentrum_Schwarzach</t>
-  </si>
-  <si>
-    <t>5451 Tenneck</t>
-  </si>
-  <si>
-    <t>Adventkonzert</t>
-  </si>
-  <si>
-    <t>https://www.salzburgervolksliedwerk.at/termine/detail?tx_calendarize_calendar%5Baction%5D=detail&amp;tx_calendarize_calendar%5Bcontroller%5D=Calendar&amp;tx_calendarize_calendar%5Bindex%5D=103822&amp;cHash=3b0ade89f12374e9bdde86e47b10ff89</t>
-  </si>
-  <si>
-    <t>5611 Großarl</t>
-  </si>
-  <si>
-    <t>Alm-Musi-Roas: Rottenhofhütte</t>
-  </si>
-  <si>
-    <t>https://www.dachstein.at/de/aktuelles/events/alm-musi-roas</t>
-  </si>
-  <si>
-    <t>5542 Flachau</t>
-  </si>
-  <si>
-    <t>Stammgäste-Galaabend im Tirolerhof</t>
-  </si>
-  <si>
-    <t>https://www.hotel-tirolerhof.com/</t>
-  </si>
-  <si>
-    <t>5550 Radstadt</t>
-  </si>
-  <si>
-    <t>Erntedankfest</t>
-  </si>
-  <si>
-    <t>https://www.radstadt.com/radstadt/veranstaltungskalender/veranstaltungen/SPO/5daeaf0a-c467-4911-8642-9265a620dec0/roem--kath--erntedankfest-mit-prozession</t>
-  </si>
-  <si>
-    <t>Musikantenstammtisch</t>
-  </si>
-  <si>
-    <t>5661 Rauris</t>
-  </si>
-  <si>
-    <t>5500 Bischofshofen</t>
-  </si>
-  <si>
-    <t>https://www.radstadt.at/Alpenlaendisches_Adventsingen</t>
-  </si>
-  <si>
-    <t>5450 Werfen</t>
-  </si>
-  <si>
-    <t>5541 Altenmarkt-Zauchensee</t>
-  </si>
-  <si>
-    <t>https://www.altenmarkt-zauchensee.at/de/winter-urlaub/advent-markt.html</t>
-  </si>
-  <si>
-    <t>Adventmarkt</t>
-  </si>
-  <si>
-    <t>5700 Zell am See</t>
-  </si>
-  <si>
-    <t>Zeller Adventkonzert des KIWANIS Club Zell am See</t>
-  </si>
-  <si>
-    <t>https://www.zellamsee-kaprun.com/de/event/zeller-adventkonzert-des-kiwanis-club-zell-am-see~12225</t>
-  </si>
-  <si>
-    <t>Weihnachtswanderung</t>
-  </si>
-  <si>
-    <t>https://www.radstadt.com/radstadt/top-events/weihnachts-wanderungen/</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="51">
+  <si>
+    <t xml:space="preserve">date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94209 Regen; Bayern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drumherum – Das Volksmusikspektakel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.drumherum.com/teilnehmer/musikanten/teilnehmer-2024-98.html?gruppe=0226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5524 Annaberg im Lammertal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rottenhofhütte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.rottenhofhuette.at/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5020 Salzburg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salzburger Straßenmusik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.salzburgervolksliedwerk.at/fileadmin/user_upload/volksliedwerk/user_upload/Folder_Salzburger_Strassenmusik_2024_web.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8966 Aich</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aicher Kirchtag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.aicher-herbst-kultur.at/Aicher_Kirtag/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5524 Annaberg im Lammertal; Winterstellgut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hochzeit (privat)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.tauroa.at/de/winterstellgut/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5453 Werfenweng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Werfenwenger Weis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.salzburgerland.com/de/werfenweng/veranstaltungen/SBG/ff809fc9-ee1b-4036-82a1-35f154d0332f/werfenwenger-herbst-weis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5620 Schwarzach im Pongau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weihnachtsfeier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.gde-schwarzach.salzburg.at/Seniorenzentrum_Schwarzach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5451 Tenneck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adventkonzert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.salzburgervolksliedwerk.at/termine/detail?tx_calendarize_calendar%5Baction%5D=detail&amp;tx_calendarize_calendar%5Bcontroller%5D=Calendar&amp;tx_calendarize_calendar%5Bindex%5D=103822&amp;cHash=3b0ade89f12374e9bdde86e47b10ff89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5611 Großarl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alm-Musi-Roas: Rottenhofhütte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.dachstein.at/de/aktuelles/events/alm-musi-roas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5542 Flachau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stammgäste-Galaabend im Tirolerhof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.hotel-tirolerhof.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5550 Radstadt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erntedankfest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.radstadt.com/radstadt/veranstaltungskalender/veranstaltungen/SPO/5daeaf0a-c467-4911-8642-9265a620dec0/roem--kath--erntedankfest-mit-prozession</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Musikantenstammtisch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5661 Rauris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5500 Bischofshofen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5541 Altenmarkt-Zauchensee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adventmarkt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.altenmarkt-zauchensee.at/de/winter-urlaub/advent-markt.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.radstadt.at/Alpenlaendisches_Adventsingen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5450 Werfen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5700 Zell am See</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zeller Adventkonzert des KIWANIS Club Zell am See</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.zellamsee-kaprun.com/de/event/zeller-adventkonzert-des-kiwanis-club-zell-am-see~12225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weihnachtswanderung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.radstadt.com/radstadt/top-events/weihnachts-wanderungen/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.stadt-salzburg.at/kultur/volkskultur/salzburger-strassenmusik/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -214,7 +231,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -222,90 +239,135 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="4285f4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="ea4335"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="fbbc04"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="34a853"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="ff6d01"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="46bdc6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="1155cc"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="1155cc"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -335,7 +397,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -359,7 +421,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -419,30 +481,29 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr defaultColWidth="12.5625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="1"/>
-    <col min="2" max="2" width="34.88671875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="34.5546875" style="2" customWidth="1"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="34.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="34.56"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -456,8 +517,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="n">
         <v>45429</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -470,8 +531,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="n">
         <v>45450</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -484,8 +545,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="n">
         <v>45493</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -498,8 +559,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="n">
         <v>45542</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -512,8 +573,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="n">
         <v>45563</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -526,8 +587,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="n">
         <v>45583</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -540,8 +601,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="n">
         <v>45617</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -554,8 +615,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="n">
         <v>45641</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -565,8 +626,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="n">
         <v>45836</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -579,8 +640,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="n">
         <v>45836</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -590,8 +651,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="n">
         <v>45844</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -604,8 +665,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="n">
         <v>45909</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -618,8 +679,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="n">
         <v>45921</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -632,8 +693,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="n">
         <v>45920</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -643,8 +704,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="n">
         <v>45948</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -654,8 +715,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="n">
         <v>45955</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -665,22 +726,22 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="n">
         <v>45998</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="n">
         <v>45998</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -689,37 +750,37 @@
       <c r="C19" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
+      <c r="D19" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="n">
         <v>46004</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>41</v>
+      <c r="B20" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="n">
         <v>46005</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
         <v>46005</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -728,12 +789,12 @@
       <c r="C22" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="0" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="n">
         <v>46017</v>
       </c>
       <c r="B23" s="2" t="s">
@@ -742,23 +803,42 @@
       <c r="C23" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="0" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="0" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D10" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="D12" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="D2" r:id="rId1" display="https://www.drumherum.com/teilnehmer/musikanten/teilnehmer-2024-98.html?gruppe=0226"/>
+    <hyperlink ref="D3" r:id="rId2" display="https://www.rottenhofhuette.at/"/>
+    <hyperlink ref="D4" r:id="rId3" display="https://www.salzburgervolksliedwerk.at/fileadmin/user_upload/volksliedwerk/user_upload/Folder_Salzburger_Strassenmusik_2024_web.pdf"/>
+    <hyperlink ref="D5" r:id="rId4" display="https://www.aicher-herbst-kultur.at/Aicher_Kirtag/"/>
+    <hyperlink ref="D6" r:id="rId5" display="https://www.tauroa.at/de/winterstellgut/"/>
+    <hyperlink ref="D7" r:id="rId6" display="https://www.salzburgerland.com/de/werfenweng/veranstaltungen/SBG/ff809fc9-ee1b-4036-82a1-35f154d0332f/werfenwenger-herbst-weis"/>
+    <hyperlink ref="D8" r:id="rId7" display="https://www.gde-schwarzach.salzburg.at/Seniorenzentrum_Schwarzach"/>
+    <hyperlink ref="D10" r:id="rId8" display="https://www.salzburgervolksliedwerk.at/termine/detail?tx_calendarize_calendar%5Baction%5D=detail&amp;tx_calendarize_calendar%5Bcontroller%5D=Calendar&amp;tx_calendarize_calendar%5Bindex%5D=103822&amp;cHash=3b0ade89f12374e9bdde86e47b10ff89"/>
+    <hyperlink ref="D12" r:id="rId9" display="https://www.dachstein.at/de/aktuelles/events/alm-musi-roas"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/termine.xlsx
+++ b/termine.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Debian\home\karin\private\almstueberlmusi.at\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B44189D5-63E3-40EE-89AF-8600AD019148}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10404" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabellenblatt1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Tabellenblatt1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -20,205 +25,199 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="51">
-  <si>
-    <t xml:space="preserve">date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">details</t>
-  </si>
-  <si>
-    <t xml:space="preserve">url</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94209 Regen; Bayern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drumherum – Das Volksmusikspektakel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.drumherum.com/teilnehmer/musikanten/teilnehmer-2024-98.html?gruppe=0226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5524 Annaberg im Lammertal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rottenhofhütte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.rottenhofhuette.at/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5020 Salzburg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salzburger Straßenmusik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.salzburgervolksliedwerk.at/fileadmin/user_upload/volksliedwerk/user_upload/Folder_Salzburger_Strassenmusik_2024_web.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8966 Aich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aicher Kirchtag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.aicher-herbst-kultur.at/Aicher_Kirtag/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5524 Annaberg im Lammertal; Winterstellgut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hochzeit (privat)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.tauroa.at/de/winterstellgut/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5453 Werfenweng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Werfenwenger Weis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.salzburgerland.com/de/werfenweng/veranstaltungen/SBG/ff809fc9-ee1b-4036-82a1-35f154d0332f/werfenwenger-herbst-weis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5620 Schwarzach im Pongau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weihnachtsfeier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.gde-schwarzach.salzburg.at/Seniorenzentrum_Schwarzach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5451 Tenneck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adventkonzert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.salzburgervolksliedwerk.at/termine/detail?tx_calendarize_calendar%5Baction%5D=detail&amp;tx_calendarize_calendar%5Bcontroller%5D=Calendar&amp;tx_calendarize_calendar%5Bindex%5D=103822&amp;cHash=3b0ade89f12374e9bdde86e47b10ff89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5611 Großarl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alm-Musi-Roas: Rottenhofhütte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.dachstein.at/de/aktuelles/events/alm-musi-roas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5542 Flachau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stammgäste-Galaabend im Tirolerhof</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.hotel-tirolerhof.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5550 Radstadt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erntedankfest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.radstadt.com/radstadt/veranstaltungskalender/veranstaltungen/SPO/5daeaf0a-c467-4911-8642-9265a620dec0/roem--kath--erntedankfest-mit-prozession</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Musikantenstammtisch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5661 Rauris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5500 Bischofshofen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5541 Altenmarkt-Zauchensee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adventmarkt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.altenmarkt-zauchensee.at/de/winter-urlaub/advent-markt.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.radstadt.at/Alpenlaendisches_Adventsingen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5450 Werfen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5700 Zell am See</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zeller Adventkonzert des KIWANIS Club Zell am See</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.zellamsee-kaprun.com/de/event/zeller-adventkonzert-des-kiwanis-club-zell-am-see~12225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weihnachtswanderung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.radstadt.com/radstadt/top-events/weihnachts-wanderungen/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.stadt-salzburg.at/kultur/volkskultur/salzburger-strassenmusik/</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="53">
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>details</t>
+  </si>
+  <si>
+    <t>url</t>
+  </si>
+  <si>
+    <t>94209 Regen; Bayern</t>
+  </si>
+  <si>
+    <t>drumherum – Das Volksmusikspektakel</t>
+  </si>
+  <si>
+    <t>https://www.drumherum.com/teilnehmer/musikanten/teilnehmer-2024-98.html?gruppe=0226</t>
+  </si>
+  <si>
+    <t>5524 Annaberg im Lammertal</t>
+  </si>
+  <si>
+    <t>Rottenhofhütte</t>
+  </si>
+  <si>
+    <t>https://www.rottenhofhuette.at/</t>
+  </si>
+  <si>
+    <t>5020 Salzburg</t>
+  </si>
+  <si>
+    <t>Salzburger Straßenmusik</t>
+  </si>
+  <si>
+    <t>https://www.salzburgervolksliedwerk.at/fileadmin/user_upload/volksliedwerk/user_upload/Folder_Salzburger_Strassenmusik_2024_web.pdf</t>
+  </si>
+  <si>
+    <t>8966 Aich</t>
+  </si>
+  <si>
+    <t>Aicher Kirchtag</t>
+  </si>
+  <si>
+    <t>https://www.aicher-herbst-kultur.at/Aicher_Kirtag/</t>
+  </si>
+  <si>
+    <t>5524 Annaberg im Lammertal; Winterstellgut</t>
+  </si>
+  <si>
+    <t>Hochzeit (privat)</t>
+  </si>
+  <si>
+    <t>https://www.tauroa.at/de/winterstellgut/</t>
+  </si>
+  <si>
+    <t>5453 Werfenweng</t>
+  </si>
+  <si>
+    <t>Werfenwenger Weis</t>
+  </si>
+  <si>
+    <t>https://www.salzburgerland.com/de/werfenweng/veranstaltungen/SBG/ff809fc9-ee1b-4036-82a1-35f154d0332f/werfenwenger-herbst-weis</t>
+  </si>
+  <si>
+    <t>5620 Schwarzach im Pongau</t>
+  </si>
+  <si>
+    <t>Weihnachtsfeier</t>
+  </si>
+  <si>
+    <t>https://www.gde-schwarzach.salzburg.at/Seniorenzentrum_Schwarzach</t>
+  </si>
+  <si>
+    <t>5451 Tenneck</t>
+  </si>
+  <si>
+    <t>Adventkonzert</t>
+  </si>
+  <si>
+    <t>https://www.salzburgervolksliedwerk.at/termine/detail?tx_calendarize_calendar%5Baction%5D=detail&amp;tx_calendarize_calendar%5Bcontroller%5D=Calendar&amp;tx_calendarize_calendar%5Bindex%5D=103822&amp;cHash=3b0ade89f12374e9bdde86e47b10ff89</t>
+  </si>
+  <si>
+    <t>5611 Großarl</t>
+  </si>
+  <si>
+    <t>Alm-Musi-Roas: Rottenhofhütte</t>
+  </si>
+  <si>
+    <t>https://www.dachstein.at/de/aktuelles/events/alm-musi-roas</t>
+  </si>
+  <si>
+    <t>5542 Flachau</t>
+  </si>
+  <si>
+    <t>Stammgäste-Galaabend im Tirolerhof</t>
+  </si>
+  <si>
+    <t>https://www.hotel-tirolerhof.com/</t>
+  </si>
+  <si>
+    <t>5550 Radstadt</t>
+  </si>
+  <si>
+    <t>Erntedankfest</t>
+  </si>
+  <si>
+    <t>https://www.radstadt.com/radstadt/veranstaltungskalender/veranstaltungen/SPO/5daeaf0a-c467-4911-8642-9265a620dec0/roem--kath--erntedankfest-mit-prozession</t>
+  </si>
+  <si>
+    <t>Musikantenstammtisch</t>
+  </si>
+  <si>
+    <t>5661 Rauris</t>
+  </si>
+  <si>
+    <t>5500 Bischofshofen</t>
+  </si>
+  <si>
+    <t>5541 Altenmarkt-Zauchensee</t>
+  </si>
+  <si>
+    <t>Adventmarkt</t>
+  </si>
+  <si>
+    <t>https://www.altenmarkt-zauchensee.at/de/winter-urlaub/advent-markt.html</t>
+  </si>
+  <si>
+    <t>https://www.radstadt.at/Alpenlaendisches_Adventsingen</t>
+  </si>
+  <si>
+    <t>5450 Werfen</t>
+  </si>
+  <si>
+    <t>5700 Zell am See</t>
+  </si>
+  <si>
+    <t>Zeller Adventkonzert des KIWANIS Club Zell am See</t>
+  </si>
+  <si>
+    <t>https://www.zellamsee-kaprun.com/de/event/zeller-adventkonzert-des-kiwanis-club-zell-am-see~12225</t>
+  </si>
+  <si>
+    <t>Weihnachtswanderung</t>
+  </si>
+  <si>
+    <t>https://www.radstadt.com/radstadt/top-events/weihnachts-wanderungen/</t>
+  </si>
+  <si>
+    <t>https://www.stadt-salzburg.at/kultur/volkskultur/salzburger-strassenmusik/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.dachstein.at/de/aktuelles/events/alm-musi-roas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://zellamsee.kiwanis.at/veranstaltungen/ </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -231,7 +230,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -239,135 +238,93 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  </cellStyleXfs>
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="2">
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285f4"/>
+        <a:srgbClr val="4285F4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ea4335"/>
+        <a:srgbClr val="EA4335"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="fbbc04"/>
+        <a:srgbClr val="FBBC04"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34a853"/>
+        <a:srgbClr val="34A853"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="ff6d01"/>
+        <a:srgbClr val="FF6D01"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46bdc6"/>
+        <a:srgbClr val="46BDC6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155cc"/>
+        <a:srgbClr val="1155CC"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155cc"/>
+        <a:srgbClr val="1155CC"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -397,7 +354,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -421,7 +378,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -481,29 +438,30 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
     <outlinePr summaryBelow="0"/>
-    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultColWidth="12.5625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="34.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="34.56"/>
+    <col min="1" max="1" width="12.5546875" style="1"/>
+    <col min="2" max="2" width="34.88671875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="34.5546875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -517,8 +475,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>45429</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -531,8 +489,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+    <row r="3" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>45450</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -545,8 +503,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+    <row r="4" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
         <v>45493</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -559,8 +517,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+    <row r="5" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
         <v>45542</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -573,8 +531,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
+    <row r="6" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
         <v>45563</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -587,8 +545,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
+    <row r="7" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
         <v>45583</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -601,8 +559,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
+    <row r="8" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
         <v>45617</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -615,8 +573,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
+    <row r="9" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
         <v>45641</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -626,8 +584,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="n">
+    <row r="10" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
         <v>45836</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -640,8 +598,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="n">
+    <row r="11" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
         <v>45836</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -651,8 +609,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="n">
+    <row r="12" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
         <v>45844</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -665,8 +623,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="n">
+    <row r="13" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
         <v>45909</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -679,8 +637,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="n">
+    <row r="14" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
         <v>45921</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -693,8 +651,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="n">
+    <row r="15" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
         <v>45920</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -704,8 +662,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="n">
+    <row r="16" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
         <v>45948</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -715,8 +673,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="n">
+    <row r="17" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
         <v>45955</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -726,8 +684,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="n">
+    <row r="18" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
         <v>45998</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -740,8 +698,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="n">
+    <row r="19" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
         <v>45998</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -754,8 +712,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="n">
+    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
         <v>46004</v>
       </c>
       <c r="B20" s="8" t="s">
@@ -765,8 +723,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="n">
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="9">
         <v>46005</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -779,8 +737,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="n">
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
         <v>46005</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -789,12 +747,12 @@
       <c r="C22" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="n">
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
         <v>46017</v>
       </c>
       <c r="B23" s="2" t="s">
@@ -803,12 +761,12 @@
       <c r="C23" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
         <v>46207</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -817,28 +775,67 @@
       <c r="C24" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>46355</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>46369</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" display="https://www.drumherum.com/teilnehmer/musikanten/teilnehmer-2024-98.html?gruppe=0226"/>
-    <hyperlink ref="D3" r:id="rId2" display="https://www.rottenhofhuette.at/"/>
-    <hyperlink ref="D4" r:id="rId3" display="https://www.salzburgervolksliedwerk.at/fileadmin/user_upload/volksliedwerk/user_upload/Folder_Salzburger_Strassenmusik_2024_web.pdf"/>
-    <hyperlink ref="D5" r:id="rId4" display="https://www.aicher-herbst-kultur.at/Aicher_Kirtag/"/>
-    <hyperlink ref="D6" r:id="rId5" display="https://www.tauroa.at/de/winterstellgut/"/>
-    <hyperlink ref="D7" r:id="rId6" display="https://www.salzburgerland.com/de/werfenweng/veranstaltungen/SBG/ff809fc9-ee1b-4036-82a1-35f154d0332f/werfenwenger-herbst-weis"/>
-    <hyperlink ref="D8" r:id="rId7" display="https://www.gde-schwarzach.salzburg.at/Seniorenzentrum_Schwarzach"/>
-    <hyperlink ref="D10" r:id="rId8" display="https://www.salzburgervolksliedwerk.at/termine/detail?tx_calendarize_calendar%5Baction%5D=detail&amp;tx_calendarize_calendar%5Bcontroller%5D=Calendar&amp;tx_calendarize_calendar%5Bindex%5D=103822&amp;cHash=3b0ade89f12374e9bdde86e47b10ff89"/>
-    <hyperlink ref="D12" r:id="rId9" display="https://www.dachstein.at/de/aktuelles/events/alm-musi-roas"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D10" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="D12" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="D25" r:id="rId10" xr:uid="{E90E9CA0-5FF7-44A9-9CF2-DC4518677DF6}"/>
+    <hyperlink ref="D27" r:id="rId11" xr:uid="{0F01FA12-B2F6-4F67-8CD1-043DCF313522}"/>
   </hyperlinks>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>